--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487942_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487942_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6839</v>
+        <v>8.5427</v>
       </c>
       <c r="E2" t="n">
-        <v>8.392099999999999</v>
+        <v>9.026199999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7081</v>
+        <v>-0.4835</v>
       </c>
       <c r="G2" t="n">
         <v>7.2141</v>
@@ -610,13 +610,13 @@
         <v>2.7751</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0911</v>
+        <v>0.9499</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1727</v>
+        <v>0.8069</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.1431</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2071</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2604</v>
+        <v>4.3492</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6066</v>
+        <v>4.7287</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3463</v>
+        <v>-0.3795</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6465</v>
+        <v>1.7552</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.9208</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2743</v>
+        <v>2.6499</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6878</v>
+        <v>4.4079</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2485</v>
+        <v>0.6999</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9363</v>
+        <v>3.708</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3343</v>
+        <v>-2.6527</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6723</v>
+        <v>-1.5946</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.662</v>
+        <v>-1.0581</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R3" t="n">
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7592</v>
+        <v>0.4552</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2886</v>
+        <v>0.303</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5294</v>
+        <v>0.1522</v>
       </c>
       <c r="V3" t="n">
-        <v>3.3547</v>
+        <v>1.5441</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6213</v>
+        <v>1.2071</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2666</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9833</v>
+        <v>4.1004</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0847</v>
+        <v>5.2221</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8986</v>
+        <v>-1.1217</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6242</v>
+        <v>-0.6465</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.033</v>
+        <v>-1.9208</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5913</v>
+        <v>1.2743</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7664</v>
+        <v>1.6878</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5655</v>
+        <v>-0.2485</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2009</v>
+        <v>1.9363</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3907</v>
+        <v>-2.3343</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5985</v>
+        <v>-1.6723</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7922</v>
+        <v>-0.662</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1805</v>
+        <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1427</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0339</v>
+        <v>0.9041</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1088</v>
+        <v>-0.3047</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4737</v>
+        <v>3.3547</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4737</v>
+        <v>3.6213</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.978</v>
+        <v>3.6349</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0021</v>
+        <v>2.8837</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9759</v>
+        <v>0.7512</v>
       </c>
       <c r="G5" t="n">
         <v>-3.6695</v>
@@ -844,13 +844,13 @@
         <v>2.9733</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8545</v>
+        <v>1.5115</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8629</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9917</v>
+        <v>0.767</v>
       </c>
       <c r="V5" t="n">
         <v>3.0178</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1077</v>
+        <v>2.6558</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9927</v>
+        <v>2.01</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8849</v>
+        <v>0.6459</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7552</v>
+        <v>-1.6242</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-1.033</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6499</v>
+        <v>-0.5913</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4079</v>
+        <v>0.7664</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6999</v>
+        <v>0.5655</v>
       </c>
       <c r="L6" t="n">
-        <v>3.708</v>
+        <v>0.2009</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6527</v>
+        <v>-2.3907</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5946</v>
+        <v>-1.5985</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0581</v>
+        <v>-0.7922</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1893</v>
       </c>
       <c r="R6" t="n">
-        <v>1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7862</v>
+        <v>1.8153</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.433</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3532</v>
+        <v>0.8561</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5441</v>
+        <v>1.4737</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2071</v>
+        <v>1.4737</v>
       </c>
       <c r="X6" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. CALDERON QUINONES</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1834</v>
+        <v>-0.1505</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0202</v>
+        <v>-1.5039</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2036</v>
+        <v>1.3534</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3816</v>
+        <v>-0.4883</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0202</v>
+        <v>-1.1905</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4018</v>
+        <v>0.7022</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0202</v>
+        <v>0.3616</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0202</v>
+        <v>-0.3292</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6908</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4018</v>
+        <v>-0.8499</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.8613</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4018</v>
+        <v>0.0114</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.7342</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.1167</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.6175</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>R. CALDERON QUINONES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2764</v>
+        <v>-0.1834</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5456</v>
+        <v>0.0202</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2692</v>
+        <v>-0.2036</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4883</v>
+        <v>-0.3816</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1905</v>
+        <v>0.0202</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7022</v>
+        <v>-0.4018</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3616</v>
+        <v>0.0202</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3292</v>
+        <v>0.0202</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6908</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8499</v>
+        <v>-0.4018</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8613</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0114</v>
+        <v>-0.4018</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3917</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9249000000000001</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5333</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. NGOM</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8234</v>
+        <v>-2.0521</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.28</v>
+        <v>-1.3241</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5435</v>
+        <v>-0.728</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5326</v>
+        <v>-2.7733</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7884</v>
+        <v>-0.7722</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7442</v>
+        <v>-2.0011</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3975</v>
+        <v>-1.8496</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0271</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4782</v>
+        <v>-1.8767</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1351</v>
+        <v>-0.9237</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8691</v>
+        <v>-0.7993</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.266</v>
+        <v>-0.1244</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5947</v>
+        <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9757</v>
+        <v>0.402</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1087</v>
+        <v>0.2589</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1329</v>
+        <v>0.1431</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8701</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8701</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>E. NGOM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9813</v>
+        <v>-2.389</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5903</v>
+        <v>-0.7893</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.391</v>
+        <v>-1.5996</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7733</v>
+        <v>-1.5326</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7722</v>
+        <v>-0.7884</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0011</v>
+        <v>-0.7442</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8496</v>
+        <v>-0.3975</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0271</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8767</v>
+        <v>-0.4782</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9237</v>
+        <v>-1.1351</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7993</v>
+        <v>-0.8691</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1244</v>
+        <v>-0.266</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1893</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4728</v>
+        <v>0.4102</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0072</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.48</v>
+        <v>-0.1891</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8701</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1367</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8443</v>
+        <v>-4.3557</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8136</v>
+        <v>-5.1565</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.8008</v>
       </c>
       <c r="G12" t="n">
         <v>-6.3912</v>
@@ -1390,13 +1390,13 @@
         <v>2.5769</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1593</v>
+        <v>0.6479</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5578</v>
+        <v>0.0993</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7171</v>
+        <v>0.5486</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.7282</v>
+        <v>14.976</v>
       </c>
       <c r="E13" t="n">
-        <v>14.4944</v>
+        <v>15.7426</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7662000000000004</v>
+        <v>-0.7663999999999997</v>
       </c>
       <c r="G13" t="n">
         <v>-7.9124</v>
@@ -1438,7 +1438,7 @@
         <v>-11.8161</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9037</v>
+        <v>3.903699999999999</v>
       </c>
       <c r="J13" t="n">
         <v>10.0177</v>
@@ -1447,7 +1447,7 @@
         <v>0.8519000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>9.165799999999999</v>
+        <v>9.165800000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-17.9301</v>
@@ -1459,7 +1459,7 @@
         <v>-5.2621</v>
       </c>
       <c r="P13" t="n">
-        <v>8.9201</v>
+        <v>8.920100000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-8.9198</v>
@@ -1468,10 +1468,10 @@
         <v>17.84</v>
       </c>
       <c r="S13" t="n">
-        <v>6.2774</v>
+        <v>7.5255</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5439</v>
+        <v>4.7919</v>
       </c>
       <c r="U13" t="n">
         <v>2.7338</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.676</v>
+        <v>7.3097</v>
       </c>
       <c r="E14" t="n">
-        <v>7.0541</v>
+        <v>6.7485</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6219</v>
+        <v>0.5611</v>
       </c>
       <c r="G14" t="n">
         <v>6.3966</v>
@@ -1546,13 +1546,13 @@
         <v>0.9911</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.333</v>
+        <v>-0.6994</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2458</v>
+        <v>-0.5514</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0873</v>
+        <v>-0.148</v>
       </c>
       <c r="V14" t="n">
         <v>1.8107</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9447</v>
+        <v>2.0779</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4739</v>
+        <v>3.2702</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5293</v>
+        <v>-1.1923</v>
       </c>
       <c r="G15" t="n">
         <v>2.5651</v>
@@ -1624,13 +1624,13 @@
         <v>0.9911</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4728</v>
+        <v>-0.3396</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1396</v>
+        <v>-0.0641</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.2754</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9405</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4494</v>
+        <v>1.1895</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0171</v>
+        <v>3.8134</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5677</v>
+        <v>-2.6239</v>
       </c>
       <c r="G17" t="n">
         <v>2.1867</v>
@@ -1780,13 +1780,13 @@
         <v>0.9911</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1843</v>
+        <v>-0.4442</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3158</v>
+        <v>0.112</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5001</v>
+        <v>-0.5562</v>
       </c>
       <c r="V17" t="n">
         <v>-1.5441</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0137</v>
+        <v>0.1718</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.0154</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1002</v>
+        <v>0.1564</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1595</v>
@@ -1858,13 +1858,13 @@
         <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.025</v>
+        <v>0.1331</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1872</v>
+        <v>-0.0853</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1622</v>
+        <v>0.2184</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8065</v>
+        <v>-0.6484</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0916</v>
+        <v>0.1934</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.898</v>
+        <v>-0.8419</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3116</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4948</v>
+        <v>-0.3368</v>
       </c>
       <c r="T19" t="n">
-        <v>0.011</v>
+        <v>0.1129</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5059</v>
+        <v>-0.4497</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0724</v>
+        <v>-1.0162</v>
       </c>
       <c r="E20" t="n">
         <v>-0.3744</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.698</v>
+        <v>-0.6419</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7355</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3369</v>
+        <v>-0.2808</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3744</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3179</v>
+        <v>-2.6562</v>
       </c>
       <c r="E21" t="n">
-        <v>0.024</v>
+        <v>-0.2816</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3419</v>
+        <v>-2.3745</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2803</v>
@@ -2092,13 +2092,13 @@
         <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3657</v>
+        <v>-0.704</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0072</v>
+        <v>-0.3128</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3585</v>
+        <v>-0.3911</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4737</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0764</v>
+        <v>-3.2215</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9223</v>
+        <v>-0.0213</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8459</v>
+        <v>-3.2002</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0557</v>
+        <v>-0.083</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4257</v>
+        <v>0.9655</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4814</v>
+        <v>-1.0485</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1798</v>
+        <v>1.4232</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1305</v>
+        <v>1.4193</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3103</v>
+        <v>0.0039</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8759</v>
+        <v>-1.5062</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2952</v>
+        <v>-0.4538</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1711</v>
+        <v>-1.0524</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.3787</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.1627</v>
+        <v>-2.9733</v>
       </c>
       <c r="R22" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6245000000000001</v>
+        <v>-0.6122</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1834</v>
+        <v>0.0552</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8079</v>
+        <v>-0.6673</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2666</v>
+        <v>-0.9405</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6036</v>
+        <v>1.4737</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8701</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7132</v>
+        <v>-3.8287</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4288</v>
+        <v>-4.0242</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2844</v>
+        <v>0.1955</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.083</v>
+        <v>-1.0557</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9655</v>
+        <v>1.4257</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0485</v>
+        <v>-2.4814</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4232</v>
+        <v>-0.1798</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4193</v>
+        <v>1.1305</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0039</v>
+        <v>-1.3103</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5062</v>
+        <v>-0.8759</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4538</v>
+        <v>0.2952</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0524</v>
+        <v>-1.1711</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5858</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9733</v>
+        <v>-4.1627</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1039</v>
+        <v>-0.1277</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3523</v>
+        <v>-0.2853</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7516</v>
+        <v>0.1575</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9405</v>
+        <v>-0.2666</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4737</v>
+        <v>0.6036</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4142</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3161</v>
+        <v>-5.1065</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1582</v>
+        <v>-4.0563</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1579</v>
+        <v>-1.0501</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3453</v>
@@ -2326,13 +2326,13 @@
         <v>0.5947</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1164</v>
+        <v>-0.9067</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9984</v>
+        <v>-0.8965</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.118</v>
+        <v>-0.0103</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2775</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.3203</v>
+        <v>-9.1311</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.735</v>
+        <v>-6.3275</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.5853</v>
+        <v>-2.8036</v>
       </c>
       <c r="G25" t="n">
         <v>-2.0758</v>
@@ -2404,13 +2404,13 @@
         <v>1.1893</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.4694</v>
+        <v>-1.2803</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8515</v>
+        <v>-0.444</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6179</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8107</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.7283</v>
+        <v>-13.049</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7661999999999995</v>
+        <v>0.7662999999999984</v>
       </c>
       <c r="F26" t="n">
-        <v>-14.4945</v>
+        <v>-13.8154</v>
       </c>
       <c r="G26" t="n">
         <v>7.912399999999999</v>
@@ -2470,7 +2470,7 @@
         <v>-0.8517999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-9.165799999999999</v>
+        <v>-9.165800000000001</v>
       </c>
       <c r="P26" t="n">
         <v>-8.920100000000001</v>
@@ -2482,19 +2482,19 @@
         <v>8.92</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.277699999999999</v>
+        <v>-5.598599999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.7338</v>
+        <v>-2.7337</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.5442</v>
+        <v>-2.8647</v>
       </c>
       <c r="V26" t="n">
         <v>-6.4429</v>
       </c>
       <c r="W26" t="n">
-        <v>3.4102</v>
+        <v>3.410200000000001</v>
       </c>
       <c r="X26" t="n">
         <v>-9.853000000000002</v>
